--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-tddui-observation-type.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-tddui-observation-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T11:03:32+00:00</t>
+    <t>2026-02-06T08:16:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-tddui-observation-type.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-tddui-observation-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-06T08:16:26+00:00</t>
+    <t>2026-02-06T09:56:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-tddui-observation-type.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-tddui-observation-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-06T09:56:58+00:00</t>
+    <t>2026-02-06T10:49:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-tddui-observation-type.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-tddui-observation-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-06T10:49:33+00:00</t>
+    <t>2026-02-10T10:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-tddui-observation-type.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-tddui-observation-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-10T10:00:25+00:00</t>
+    <t>2026-02-11T15:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-tddui-observation-type.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-tddui-observation-type.xlsx
@@ -8,12 +8,13 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
+    <sheet name="Include #1" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="39">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T15:08:15+00:00</t>
+    <t>2026-02-12T14:50:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -112,6 +113,24 @@
   </si>
   <si>
     <t>https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-observation-type</t>
+  </si>
+  <si>
+    <t>Concept</t>
+  </si>
+  <si>
+    <t>79378-6</t>
+  </si>
+  <si>
+    <t>Cause of death</t>
+  </si>
+  <si>
+    <t>LP73551-1</t>
+  </si>
+  <si>
+    <t>Transport mode</t>
+  </si>
+  <si>
+    <t>http://loinc.org</t>
   </si>
 </sst>
 </file>
@@ -411,4 +430,58 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>33</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-tddui-observation-type.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-tddui-observation-type.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-12T14:50:08+00:00</t>
+    <t>2026-02-16T09:17:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-tddui-observation-type.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-tddui-observation-type.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T09:17:35+00:00</t>
+    <t>2026-02-16T09:32:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-tddui-observation-type.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-tddui-observation-type.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T09:32:48+00:00</t>
+    <t>2026-02-16T14:58:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-tddui-observation-type.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-tddui-observation-type.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T14:58:48+00:00</t>
+    <t>2026-02-23T15:44:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -85,7 +85,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>ValueSet for the Observation types.</t>
+    <t>ValueSet pour les types d'Observation.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-tddui-observation-type.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-tddui-observation-type.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T15:44:46+00:00</t>
+    <t>2026-02-24T10:21:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-tddui-observation-type.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-tddui-observation-type.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0-ballot</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-24T10:21:42+00:00</t>
+    <t>2026-02-24T16:53:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-tddui-observation-type.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-tddui-observation-type.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>2.2.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-24T16:53:25+00:00</t>
+    <t>2026-02-25T09:45:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-tddui-observation-type.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-tddui-observation-type.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0-ballot</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-25T09:45:56+00:00</t>
+    <t>2026-02-26T08:21:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-tddui-observation-type.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-tddui-observation-type.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T08:21:36+00:00</t>
+    <t>2026-02-26T10:20:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
